--- a/운동프로그램_재편_v14.xlsx
+++ b/운동프로그램_재편_v14.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_148EEDE9F63BFAE9F2A31C48984BBC82CDA4EADC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C59D599-2997-4763-BA96-A93E7EA38BE7}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_148EEDE9F63BFAE9F2A31C48984BBC82CDA4EADC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{345D1AF2-535D-40C8-A7BD-9BDBDBBA8653}"/>
   <bookViews>
-    <workbookView xWindow="6690" yWindow="1635" windowWidth="29670" windowHeight="18480" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6690" yWindow="1635" windowWidth="29670" windowHeight="18480" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -15930,6 +15930,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -18392,7 +18396,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="276" customHeight="1">
+    <row r="19" spans="1:9" ht="77.25" customHeight="1">
       <c r="A19" s="6" t="s">
         <v>114</v>
       </c>
@@ -18421,7 +18425,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="300" customHeight="1">
+    <row r="20" spans="1:9" ht="48" customHeight="1">
       <c r="A20" s="26">
         <v>1</v>
       </c>
@@ -18451,7 +18455,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="252" customHeight="1">
+    <row r="21" spans="1:9" ht="43.5" customHeight="1">
       <c r="A21" s="7">
         <v>2</v>
       </c>
@@ -18480,7 +18484,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="240" customHeight="1">
+    <row r="22" spans="1:9" ht="48.75" customHeight="1">
       <c r="A22" s="7">
         <v>3</v>
       </c>
@@ -18507,7 +18511,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="212.25" customHeight="1">
+    <row r="23" spans="1:9" ht="33.75" customHeight="1">
       <c r="A23" s="7">
         <v>4</v>
       </c>
@@ -18563,7 +18567,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="105" customHeight="1">
+    <row r="25" spans="1:9" ht="38.25" customHeight="1">
       <c r="D25" s="30" t="s">
         <v>146</v>
       </c>
@@ -20328,7 +20332,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="228" customHeight="1">
+    <row r="19" spans="1:9" ht="49.5" customHeight="1">
       <c r="D19" s="30" t="s">
         <v>146</v>
       </c>

--- a/운동프로그램_재편_v14.xlsx
+++ b/운동프로그램_재편_v14.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_148EEDE9F63BFAE9F2A31C48984BBC82CDA4EADC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{345D1AF2-535D-40C8-A7BD-9BDBDBBA8653}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_148EEDE9F63BFAE9F2A31C48984BBC82CDA4EADC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7666FE3B-6206-4665-BCFE-A7EFF6ED7B32}"/>
   <bookViews>
-    <workbookView xWindow="6690" yWindow="1635" windowWidth="29670" windowHeight="18480" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="576">
   <si>
     <t>시작 중량 설정 — 5년 공백 후 복귀</t>
   </si>
@@ -2103,9 +2103,6 @@
     <t>둔근 · 팔 · 복부</t>
   </si>
   <si>
-    <t>둔근 · 이두 · 삼두 · 복부</t>
-  </si>
-  <si>
     <t>일</t>
   </si>
   <si>
@@ -7537,9 +7534,6 @@
     <t>종아리</t>
   </si>
   <si>
-    <t>원본에 종아리 종목이 전무했음</t>
-  </si>
-  <si>
     <t>스탠딩 카프 레이즈 머신 (무릎 편 상태 — 비복근) / 시티드 카프 레이즈 (무릎 굽힘 — 가자미근) / 레그 프레스 발판 끝에서 카프 레이즈 / 스미스 카프 레이즈</t>
   </si>
   <si>
@@ -8155,9 +8149,6 @@
     <t>토요일 — 둔근 · 팔 · 복부</t>
   </si>
   <si>
-    <t>서로 회복 경쟁이 없는 조합. 그 주 가장 가벼운 세션. 순서: 둔근 → 팔 → 복부</t>
-  </si>
-  <si>
     <t>힙 쓰러스트</t>
   </si>
   <si>
@@ -9433,6 +9424,81 @@
     </r>
   </si>
   <si>
+    <t>근육군별 주간 세트 — 검산</t>
+  </si>
+  <si>
+    <t>세트는 근육군 단위로 센다. '하체 20세트'는 의미 없는 숫자 — 대퇴 18 / 햄스트링 2여도 하체 20이 된다.</t>
+  </si>
+  <si>
+    <t>직접 세트</t>
+  </si>
+  <si>
+    <t>간접 추정</t>
+  </si>
+  <si>
+    <t>실질</t>
+  </si>
+  <si>
+    <t>판정</t>
+  </si>
+  <si>
+    <t>간접 출처 / 비고</t>
+  </si>
+  <si>
+    <t>플랫 벤치 5세트가 쇄골지에도 일부 기여</t>
+  </si>
+  <si>
+    <t>인클라인 6세트가 흉늑지에도 일부 기여</t>
+  </si>
+  <si>
+    <t>데드리프트 간접</t>
+  </si>
+  <si>
+    <t>친업 · 랫풀다운의 견갑골 하강 — 동작 개시에만 관여하므로 하향 (5 → 3)</t>
+  </si>
+  <si>
+    <t>승모(중부)·능형근</t>
+  </si>
+  <si>
+    <t>바벨 로우 4 · 30도 인클라인 로우 3 · 벤트오버 레터럴 4 — 전부 견갑골 후인. 직접 종목은 없으므로 로우를 빼면 이 칸도 함께 내릴 것</t>
+  </si>
+  <si>
+    <t>스쿼트 · RDL · 바벨로우</t>
+  </si>
+  <si>
+    <t>벤치 · 인클라인 · 딥스</t>
+  </si>
+  <si>
+    <t>바벨 로우 · 인클라인 로우</t>
+  </si>
+  <si>
+    <t>데드리프트 · 힙 쓰러스트</t>
+  </si>
+  <si>
+    <t>스쿼트 · RDL · 데드</t>
+  </si>
+  <si>
+    <t>불가리안 스플릿 스쿼트 · 스쿼트 · 런지의 관상면 안정화 (한 다리 지지 구간)</t>
+  </si>
+  <si>
+    <t>친업 · 바벨로우 · 덤벨로우</t>
+  </si>
+  <si>
+    <t>벤치 · 프레스 · 딥스</t>
+  </si>
+  <si>
+    <t>데드 105kg · 로우 · 친업 그립</t>
+  </si>
+  <si>
+    <t>스쿼트 · 데드 코어 안정화</t>
+  </si>
+  <si>
+    <t>직접 세트 총계</t>
+  </si>
+  <si>
+    <t>기준선</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i/>
@@ -9452,7 +9518,441 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>덤벨 사이드 밴드도 원본에 있으나</t>
+      <t xml:space="preserve">주 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>10~20</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세트 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>성장 구간</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세트 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>유지 하한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실패지점 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>2~3</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회 이내 세트만 카운트 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">웜업 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>여유 세트 제외</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>따로 세야 하는 경우</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>판단 기준은 하나 — 다른 종목이 그 부위를 대신 키워주는가</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>안 키워주면 따로 센다</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>햄스트링</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>스쿼트로 안 자람</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>후면 삼각근</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>프레스로 안 자람</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>종아리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>키워주면 합쳐 센다</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>흉근 상</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>하</t>
     </r>
     <r>
       <rPr>
@@ -9473,529 +9973,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>허리 측면에 무게를 직접 얹어 부담이 크므로 회전을 우선</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>근육군별 주간 세트 — 검산</t>
-  </si>
-  <si>
-    <t>세트는 근육군 단위로 센다. '하체 20세트'는 의미 없는 숫자 — 대퇴 18 / 햄스트링 2여도 하체 20이 된다.</t>
-  </si>
-  <si>
-    <t>직접 세트</t>
-  </si>
-  <si>
-    <t>간접 추정</t>
-  </si>
-  <si>
-    <t>실질</t>
-  </si>
-  <si>
-    <t>판정</t>
-  </si>
-  <si>
-    <t>간접 출처 / 비고</t>
-  </si>
-  <si>
-    <t>플랫 벤치 5세트가 쇄골지에도 일부 기여</t>
-  </si>
-  <si>
-    <t>인클라인 6세트가 흉늑지에도 일부 기여</t>
-  </si>
-  <si>
-    <t>데드리프트 간접</t>
-  </si>
-  <si>
-    <t>친업 · 랫풀다운의 견갑골 하강 — 동작 개시에만 관여하므로 하향 (5 → 3)</t>
-  </si>
-  <si>
-    <t>승모(중부)·능형근</t>
-  </si>
-  <si>
-    <t>바벨 로우 4 · 30도 인클라인 로우 3 · 벤트오버 레터럴 4 — 전부 견갑골 후인. 직접 종목은 없으므로 로우를 빼면 이 칸도 함께 내릴 것</t>
-  </si>
-  <si>
-    <t>스쿼트 · RDL · 바벨로우</t>
-  </si>
-  <si>
-    <t>벤치 · 인클라인 · 딥스</t>
-  </si>
-  <si>
-    <t>바벨 로우 · 인클라인 로우</t>
-  </si>
-  <si>
-    <t>데드리프트 · 힙 쓰러스트</t>
-  </si>
-  <si>
-    <t>스쿼트 · RDL · 데드</t>
-  </si>
-  <si>
-    <t>불가리안 스플릿 스쿼트 · 스쿼트 · 런지의 관상면 안정화 (한 다리 지지 구간)</t>
-  </si>
-  <si>
-    <t>친업 · 바벨로우 · 덤벨로우</t>
-  </si>
-  <si>
-    <t>벤치 · 프레스 · 딥스</t>
-  </si>
-  <si>
-    <t>데드 105kg · 로우 · 친업 그립</t>
-  </si>
-  <si>
-    <t>스쿼트 · 데드 코어 안정화</t>
-  </si>
-  <si>
-    <t>직접 세트 총계</t>
-  </si>
-  <si>
-    <t>기준선</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>10~20</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">세트 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>성장 구간</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">세트 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>유지 하한</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실패지점 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2~3</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회 이내 세트만 카운트 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">웜업 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>여유 세트 제외</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>따로 세야 하는 경우</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>판단 기준은 하나 — 다른 종목이 그 부위를 대신 키워주는가</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>안 키워주면 따로 센다</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>햄스트링</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>스쿼트로 안 자람</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>후면 삼각근</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>프레스로 안 자람</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>종아리</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>키워주면 합쳐 센다</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>흉근 상</t>
+      <t>광배 상</t>
     </r>
     <r>
       <rPr>
@@ -10016,160 +9994,11 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>하</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>광배 상</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t>하 — 하나의 근육이며 함께 수축한다</t>
     </r>
   </si>
   <si>
     <t>현재 보완 필요 항목</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종아리 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>세트 — 하한 미달</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>우선순위 낮아 현재는 유지</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신경 쓰이면 토요일에 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2~3</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>세트 추가</t>
-    </r>
   </si>
   <si>
     <r>
@@ -15527,6 +15356,49 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>원본에 종아리 종목이 전무했음. 3→4세트 증량 (RP MEV 대조) — 무릎 편 스탠딩 계열로, 토요일 시티드와 구분</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>서로 회복 경쟁이 없는 조합. 그 주 가장 가벼운 세션. 순서: 둔근 → 팔 → 복부 → 종아리</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>시티드 카프 레이즈</t>
+  </si>
+  <si>
+    <t>신규 추가 (RP 볼륨 대조 — 주 3세트는 MEV 미달). 무릎을 굽히면 비복근이 느슨해져 가자미근이 주도 — 금요일 스탠딩과 역할이 다름. 금 4세트와 합쳐 주 8세트</t>
+  </si>
+  <si>
+    <t>시티드 카프 레이즈 머신 (1순위) / 레그 프레스에서 무릎 굽힌 채 발끝으로 밀기 / 덤벨을 무릎에 올리고 발뒤꿈치 들기 (집에서) / 머신이 없으면 스탠딩으로 하되 금요일과 각도를 다르게</t>
+  </si>
+  <si>
+    <t>종아리 추가 (2026-08 · RP 볼륨 대조)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 주 3세트는 유지 하한(8세트) 미달 — 검산표에서 유일한 실질 미달 부위였다. 금 카프 4 + 토 시티드 4 = 주 8세트.</t>
+  </si>
+  <si>
+    <t>· 스탠딩(무릎 폄)은 비복근, 시티드(무릎 굽힘)는 가자미근 주도 — 둘을 나눠야 종아리 전체가 커버된다.</t>
+  </si>
+  <si>
+    <t>금 스탠딩 4 · 토 시티드 4 — 무릎 각도로 비복근/가자미근 분담 (2026-08 보강)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 종아리 보강 완료 (2026-08): 금 카프 4 + 토 시티드 카프 4 = 주 8세트 — 유지 하한 충족. 더 키우려면 10세트부터.</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>둔근 · 이두 · 삼두 · 복부 · 종아리</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>약 60분</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -15737,7 +15609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -15844,6 +15716,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16667,23 +16548,23 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="40" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -16691,10 +16572,10 @@
         <v>69</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
@@ -16702,91 +16583,91 @@
         <v>75</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="28" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="28" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -16794,17 +16675,17 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -16828,17 +16709,17 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="41" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
@@ -16846,19 +16727,19 @@
         <v>55</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
@@ -16866,10 +16747,10 @@
         <v>60</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>72</v>
@@ -16878,7 +16759,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
@@ -16886,20 +16767,20 @@
         <v>64</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_화_상체밀기!$E$10</f>
         <v>19</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
@@ -16907,10 +16788,10 @@
         <v>68</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>72</v>
@@ -16919,7 +16800,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
@@ -16927,10 +16808,10 @@
         <v>71</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>72</v>
@@ -16939,7 +16820,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
@@ -16947,10 +16828,10 @@
         <v>74</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>72</v>
@@ -16959,7 +16840,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
@@ -16967,10 +16848,10 @@
         <v>78</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D11" s="28" t="s">
         <v>75</v>
@@ -16980,18 +16861,18 @@
         <v>15</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="D12" s="28" t="s">
         <v>69</v>
@@ -17001,12 +16882,12 @@
         <v>13</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
       <c r="A13" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
@@ -17019,27 +16900,27 @@
     </row>
     <row r="15" spans="1:6" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
@@ -17047,32 +16928,32 @@
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
@@ -17080,27 +16961,27 @@
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -17127,38 +17008,38 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>116</v>
-      </c>
       <c r="G4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -17169,22 +17050,22 @@
         <v>14</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E5" s="28">
         <v>5</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -17192,10 +17073,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>73</v>
@@ -17204,13 +17085,13 @@
         <v>3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
@@ -17218,10 +17099,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>132</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>133</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>73</v>
@@ -17230,11 +17111,11 @@
         <v>3</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G7" s="18"/>
       <c r="H7" s="18" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
@@ -17242,25 +17123,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>165</v>
-      </c>
       <c r="D8" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E8" s="7">
         <v>4</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
@@ -17268,30 +17149,30 @@
         <v>5</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>168</v>
-      </c>
       <c r="D9" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9" s="7">
         <v>4</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="D10" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E10" s="22">
         <f>SUM(E5:E9)</f>
@@ -17300,22 +17181,22 @@
     </row>
     <row r="12" spans="1:8" ht="32.25" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="278.25" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="237.75" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="237.75" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -17342,38 +17223,38 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>116</v>
-      </c>
       <c r="G4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29.25" customHeight="1">
@@ -17384,22 +17265,22 @@
         <v>10</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E5" s="28">
         <v>3</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -17407,10 +17288,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>73</v>
@@ -17419,13 +17300,13 @@
         <v>3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
@@ -17433,10 +17314,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>73</v>
@@ -17445,13 +17326,13 @@
         <v>3</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
@@ -17459,10 +17340,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>73</v>
@@ -17471,11 +17352,11 @@
         <v>3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="18" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
@@ -17486,27 +17367,27 @@
         <v>15</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="D10" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E10" s="22">
         <f>SUM(E5:E9)</f>
@@ -17515,22 +17396,22 @@
     </row>
     <row r="12" spans="1:8" ht="76.5" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="265.5" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="293.25" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="276" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -17557,38 +17438,38 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>116</v>
-      </c>
       <c r="G4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29.25" customHeight="1">
@@ -17599,22 +17480,22 @@
         <v>12</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="E5" s="28">
         <v>1</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -17622,10 +17503,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>73</v>
@@ -17634,13 +17515,13 @@
         <v>3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
@@ -17648,25 +17529,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E7" s="7">
         <v>3</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
@@ -17674,10 +17555,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>73</v>
@@ -17686,13 +17567,13 @@
         <v>3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
@@ -17700,30 +17581,30 @@
         <v>5</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>183</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="D10" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E10" s="22">
         <f>SUM(E5:E9)</f>
@@ -17732,22 +17613,22 @@
     </row>
     <row r="12" spans="1:8" ht="92.25" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="233.25" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="240" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="278.25" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
@@ -17755,22 +17636,22 @@
     </row>
     <row r="17" spans="1:1" ht="95.25" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="252.75" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="237.75" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="265.5" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -17792,96 +17673,96 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
@@ -17889,13 +17770,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
@@ -17903,52 +17784,52 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="39" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
@@ -17956,12 +17837,12 @@
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
@@ -17969,12 +17850,12 @@
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -18105,7 +17986,7 @@
       </c>
       <c r="D9" s="7">
         <f>금_하체!$E$19</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>77</v>
@@ -18119,19 +18000,19 @@
         <v>79</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>80</v>
+        <v>574</v>
       </c>
       <c r="D10" s="7">
-        <f>토_둔근팔복부!$E$19</f>
-        <v>31</v>
+        <f>토_둔근팔복부!$E$21</f>
+        <v>35</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>63</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
       <c r="A11" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>72</v>
@@ -18148,84 +18029,84 @@
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
       <c r="A12" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="23"/>
       <c r="D12" s="22">
         <f>SUM(D5:D11)</f>
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E12" s="22"/>
     </row>
     <row r="14" spans="1:5" ht="16.5" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="89.25" customHeight="1">
       <c r="A15" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="76.5" customHeight="1">
       <c r="A16" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="38.25" customHeight="1">
       <c r="A17" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="114.75" customHeight="1">
       <c r="A18" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="79.5" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="64.5" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="90" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="102.75" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="100.5" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15" customHeight="1">
@@ -18233,22 +18114,22 @@
     </row>
     <row r="34" spans="1:1" ht="90" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="51.75" customHeight="1">
       <c r="A35" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="77.25" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="64.5" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -18276,23 +18157,23 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -18357,72 +18238,72 @@
     </row>
     <row r="10" spans="1:3" ht="252.75" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25.5" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25.5" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1"/>
     <row r="18" spans="1:9" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="77.25" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="48" customHeight="1">
@@ -18430,10 +18311,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>120</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>121</v>
       </c>
       <c r="D20" s="29">
         <f>시작중량_설정!$E$9</f>
@@ -18443,16 +18324,16 @@
         <v>5</v>
       </c>
       <c r="F20" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="H20" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="H20" s="27" t="s">
+      <c r="I20" s="18" t="s">
         <v>124</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="43.5" customHeight="1">
@@ -18460,28 +18341,28 @@
         <v>2</v>
       </c>
       <c r="B21" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>126</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>127</v>
       </c>
       <c r="E21" s="7">
         <v>3</v>
       </c>
       <c r="F21" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="H21" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="I21" s="18" t="s">
         <v>130</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="48.75" customHeight="1">
@@ -18489,26 +18370,26 @@
         <v>3</v>
       </c>
       <c r="B22" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>133</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>134</v>
       </c>
       <c r="E22" s="7">
         <v>3</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="33.75" customHeight="1">
@@ -18516,26 +18397,26 @@
         <v>4</v>
       </c>
       <c r="B23" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>138</v>
       </c>
       <c r="E23" s="7">
         <v>4</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G23" s="18"/>
       <c r="H23" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" s="18" t="s">
         <v>140</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
@@ -18543,33 +18424,33 @@
         <v>5</v>
       </c>
       <c r="B24" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>143</v>
       </c>
       <c r="E24" s="7">
         <v>3</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H24" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="18" t="s">
         <v>144</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="38.25" customHeight="1">
       <c r="D25" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" s="22">
         <f>SUM(E20:E24)</f>
@@ -18579,22 +18460,22 @@
     <row r="26" spans="1:9" ht="305.25" customHeight="1"/>
     <row r="27" spans="1:9" ht="278.25" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="141" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="265.5" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="330.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1">
@@ -18602,32 +18483,32 @@
     </row>
     <row r="32" spans="1:9" ht="328.5" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="168">
       <c r="A33" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="144">
       <c r="A34" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="84">
       <c r="A35" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="144">
       <c r="A36" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="180">
       <c r="A37" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -18635,7 +18516,7 @@
     </row>
     <row r="39" spans="1:1" ht="204">
       <c r="A39" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -18663,23 +18544,23 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -18744,72 +18625,72 @@
     </row>
     <row r="10" spans="1:3" ht="252.75" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25.5" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1"/>
     <row r="18" spans="1:9" ht="25.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="25.5" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="33.75" customHeight="1">
@@ -18817,10 +18698,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>160</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>161</v>
       </c>
       <c r="D20" s="29">
         <f>시작중량_설정!$E$10</f>
@@ -18830,16 +18711,16 @@
         <v>3</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G20" s="27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H20" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="I20" s="18" t="s">
         <v>162</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="51" customHeight="1">
@@ -18847,24 +18728,24 @@
         <v>2</v>
       </c>
       <c r="B21" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>165</v>
-      </c>
       <c r="D21" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E21" s="7">
         <v>4</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" customHeight="1">
@@ -18872,24 +18753,24 @@
         <v>3</v>
       </c>
       <c r="B22" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>168</v>
-      </c>
       <c r="D22" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E22" s="7">
         <v>4</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="46.5" customHeight="1">
@@ -18897,10 +18778,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D23" s="7">
         <v>15</v>
@@ -18909,16 +18790,16 @@
         <v>3</v>
       </c>
       <c r="F23" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="H23" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="H23" s="18" t="s">
+      <c r="I23" s="18" t="s">
         <v>173</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="48" customHeight="1">
@@ -18926,26 +18807,26 @@
         <v>5</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E24" s="7">
         <v>3</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H24" s="18"/>
       <c r="I24" s="18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1">
@@ -18953,26 +18834,26 @@
         <v>6</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E25" s="7">
         <v>3</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G25" s="18"/>
       <c r="H25" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="I25" s="18" t="s">
         <v>179</v>
-      </c>
-      <c r="I25" s="18" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="42" customHeight="1">
@@ -18980,33 +18861,33 @@
         <v>7</v>
       </c>
       <c r="B26" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>183</v>
       </c>
       <c r="E26" s="7">
         <v>2</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G26" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="H26" s="18" t="s">
+      <c r="I26" s="18" t="s">
         <v>185</v>
-      </c>
-      <c r="I26" s="18" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="57.75" customHeight="1">
       <c r="D27" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E27" s="22">
         <f>SUM(E20:E26)</f>
@@ -19016,22 +18897,22 @@
     <row r="28" spans="1:9" ht="276" customHeight="1"/>
     <row r="29" spans="1:9" ht="252" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="240" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="153" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="156">
       <c r="A32" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -19039,27 +18920,27 @@
     </row>
     <row r="34" spans="1:1" ht="48">
       <c r="A34" s="31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="168">
       <c r="A35" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="168">
       <c r="A36" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="156">
       <c r="A37" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="156">
       <c r="A38" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -19087,23 +18968,23 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
@@ -19168,41 +19049,41 @@
     </row>
     <row r="10" spans="1:9" ht="252.75" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
@@ -19210,10 +19091,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>198</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>199</v>
       </c>
       <c r="D13" s="29">
         <f>시작중량_설정!$E$8</f>
@@ -19223,16 +19104,16 @@
         <v>1</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G13" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="H13" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="H13" s="27" t="s">
+      <c r="I13" s="18" t="s">
         <v>201</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
@@ -19240,28 +19121,28 @@
         <v>2</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>204</v>
       </c>
       <c r="E14" s="7">
         <v>4</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G14" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="I14" s="18" t="s">
         <v>206</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
@@ -19269,28 +19150,28 @@
         <v>3</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E15" s="7">
         <v>3</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G15" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="H15" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="I15" s="18" t="s">
         <v>210</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
@@ -19298,28 +19179,28 @@
         <v>4</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E16" s="7">
         <v>4</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="H16" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="H16" s="18" t="s">
+      <c r="I16" s="18" t="s">
         <v>215</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
@@ -19327,10 +19208,10 @@
         <v>5</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>73</v>
@@ -19339,16 +19220,16 @@
         <v>3</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H17" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="I17" s="18" t="s">
         <v>218</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
@@ -19356,10 +19237,10 @@
         <v>6</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D18" s="7">
         <v>20</v>
@@ -19368,14 +19249,14 @@
         <v>3</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H18" s="18"/>
       <c r="I18" s="32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
@@ -19383,33 +19264,33 @@
         <v>7</v>
       </c>
       <c r="B19" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>183</v>
       </c>
       <c r="E19" s="7">
         <v>3</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H19" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="I19" s="18" t="s">
         <v>223</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="276" customHeight="1">
       <c r="D20" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E20" s="22">
         <f>SUM(E13:E19)</f>
@@ -19419,22 +19300,22 @@
     <row r="21" spans="1:9" ht="108" customHeight="1"/>
     <row r="22" spans="1:9" ht="240" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="204" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="79.5" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="201.75" customHeight="1">
@@ -19442,42 +19323,42 @@
     </row>
     <row r="27" spans="1:9" ht="229.5" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="255" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="165.75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="235.5" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="222.75" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="328.5" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="265.5" customHeight="1">
@@ -19485,17 +19366,17 @@
     </row>
     <row r="36" spans="1:1" ht="375" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="375" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="141" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15" customHeight="1">
@@ -19503,42 +19384,42 @@
     </row>
     <row r="41" spans="1:1" ht="63.75" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="128.25" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="153" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="141" customHeight="1">
       <c r="A44" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="165.75" customHeight="1">
       <c r="A45" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="115.5" customHeight="1">
       <c r="A46" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="102.75" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="165.75" customHeight="1">
       <c r="A48" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -19566,23 +19447,23 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
@@ -19647,41 +19528,41 @@
     </row>
     <row r="10" spans="1:9" ht="252.75" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="25.5" customHeight="1">
@@ -19689,10 +19570,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>250</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>251</v>
       </c>
       <c r="D13" s="29">
         <f>시작중량_설정!$E$7</f>
@@ -19702,16 +19583,16 @@
         <v>5</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G13" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="H13" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="H13" s="27" t="s">
+      <c r="I13" s="18" t="s">
         <v>253</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
@@ -19719,10 +19600,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="D14" s="7">
         <v>70</v>
@@ -19731,16 +19612,16 @@
         <v>4</v>
       </c>
       <c r="F14" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="G14" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="H14" s="18" t="s">
+      <c r="I14" s="18" t="s">
         <v>258</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
@@ -19748,10 +19629,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>73</v>
@@ -19760,16 +19641,16 @@
         <v>3</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G15" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="H15" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="I15" s="18" t="s">
         <v>262</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
@@ -19777,10 +19658,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>73</v>
@@ -19789,14 +19670,14 @@
         <v>4</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="I16" s="18" t="s">
         <v>265</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="25.5" customHeight="1">
@@ -19804,28 +19685,28 @@
         <v>5</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E17" s="7">
         <v>3</v>
       </c>
       <c r="F17" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="H17" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="G17" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="H17" s="18" t="s">
+      <c r="I17" s="18" t="s">
         <v>269</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
@@ -19833,60 +19714,60 @@
         <v>6</v>
       </c>
       <c r="B18" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>73</v>
       </c>
       <c r="E18" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="18" t="s">
-        <v>273</v>
+        <v>564</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
       <c r="D19" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" s="22">
         <f>SUM(E13:E18)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="48" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="96" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="120" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="96" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="96" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1">
@@ -19894,27 +19775,27 @@
     </row>
     <row r="27" spans="1:9" ht="204" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="228" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="204" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="293.25" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1">
@@ -19922,17 +19803,17 @@
     </row>
     <row r="33" spans="1:1" ht="305.25" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="229.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="341.25" customHeight="1">
       <c r="A35" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -19944,7 +19825,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -19960,46 +19841,46 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>289</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
@@ -20014,28 +19895,28 @@
         <v>1</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E6" s="7">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1">
@@ -20043,10 +19924,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D7" s="7">
         <v>15</v>
@@ -20055,16 +19936,16 @@
         <v>3</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
@@ -20072,10 +19953,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>73</v>
@@ -20084,19 +19965,19 @@
         <v>3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="18" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
       <c r="A9" s="33" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -20111,28 +19992,28 @@
         <v>4</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I10" s="32" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
@@ -20140,26 +20021,26 @@
         <v>5</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E11" s="7">
         <v>3</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="18" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
@@ -20167,10 +20048,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D12" s="7">
         <v>10</v>
@@ -20179,14 +20060,14 @@
         <v>3</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="18" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
@@ -20194,10 +20075,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D13" s="7">
         <v>10</v>
@@ -20206,19 +20087,19 @@
         <v>2</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G13" s="18"/>
       <c r="H13" s="18" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="33" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -20233,24 +20114,24 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E15" s="7">
         <v>3</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
@@ -20258,10 +20139,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D16" s="7">
         <v>2.5</v>
@@ -20270,12 +20151,12 @@
         <v>3</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
@@ -20283,10 +20164,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>73</v>
@@ -20295,14 +20176,14 @@
         <v>2</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="18" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="29.25" customHeight="1">
@@ -20310,10 +20191,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>73</v>
@@ -20322,77 +20203,127 @@
         <v>3</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A19" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="B19" s="44"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+    </row>
+    <row r="20" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A20" s="43">
+        <v>12</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>566</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="D20" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44" t="s">
+        <v>567</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="49.5" customHeight="1">
+      <c r="D21" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" s="22">
+        <f>SUM(E5:E20)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="252" customHeight="1"/>
+    <row r="23" spans="1:9" ht="240" customHeight="1">
+      <c r="A23" s="11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="276" customHeight="1">
+      <c r="A24" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="I18" s="18" t="s">
+    </row>
+    <row r="25" spans="1:9" ht="265.5" customHeight="1">
+      <c r="A25" s="11" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="49.5" customHeight="1">
-      <c r="D19" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" s="22">
-        <f>SUM(E5:E18)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="252" customHeight="1"/>
-    <row r="21" spans="1:9" ht="240" customHeight="1">
-      <c r="A21" s="11" t="s">
+    <row r="26" spans="1:9" ht="293.25" customHeight="1">
+      <c r="A26" s="11" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="276" customHeight="1">
-      <c r="A22" s="11" t="s">
+    <row r="27" spans="1:9" ht="15" customHeight="1">
+      <c r="A27" s="31"/>
+    </row>
+    <row r="28" spans="1:9" ht="60.75" customHeight="1">
+      <c r="A28" s="13" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="265.5" customHeight="1">
-      <c r="A23" s="11" t="s">
+    <row r="29" spans="1:9" ht="303" customHeight="1">
+      <c r="A29" s="11" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="293.25" customHeight="1">
-      <c r="A24" s="11" t="s">
+    <row r="30" spans="1:9" ht="291" customHeight="1">
+      <c r="A30" s="11" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1">
-      <c r="A25" s="31"/>
-    </row>
-    <row r="26" spans="1:9" ht="60.75" customHeight="1">
-      <c r="A26" s="13" t="s">
+    <row r="31" spans="1:9" ht="278.25" customHeight="1">
+      <c r="A31" s="11" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="303" customHeight="1">
-      <c r="A27" s="11" t="s">
+    <row r="32" spans="1:9" ht="227.25" customHeight="1">
+      <c r="A32" s="11" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="291" customHeight="1">
-      <c r="A28" s="11" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="278.25" customHeight="1">
-      <c r="A29" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="227.25" customHeight="1">
-      <c r="A30" s="11" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="293.25" customHeight="1">
-      <c r="A31" s="11" t="s">
-        <v>341</v>
+    <row r="33" spans="1:1" ht="293.25" customHeight="1">
+      <c r="A33" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -20416,37 +20347,37 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A5)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A5)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A5)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A5)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A5)</f>
@@ -20464,12 +20395,12 @@
         <v>충분</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B6" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A6)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A6)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A6)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A6)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A6)</f>
@@ -20487,12 +20418,12 @@
         <v>충분</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B7" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A7)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A7)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A7)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A7)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A7)</f>
@@ -20510,12 +20441,12 @@
         <v>충분</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A8)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A8)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A8)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A8)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A8)</f>
@@ -20533,12 +20464,12 @@
         <v>충분</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B9" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A9)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A9)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A9)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A9)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A9)</f>
@@ -20556,12 +20487,12 @@
         <v>충분</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B10" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A10)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A10)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A10)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A10)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A10)</f>
@@ -20579,12 +20510,12 @@
         <v>충분</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B11" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A11)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A11)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A11)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A11)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A11)</f>
@@ -20602,12 +20533,12 @@
         <v>충분</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B12" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A12)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A12)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A12)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A12)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A12)</f>
@@ -20630,7 +20561,7 @@
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B13" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A13)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A13)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A13)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A13)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A13)</f>
@@ -20648,12 +20579,12 @@
         <v>충분</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B14" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A14)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A14)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A14)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A14)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A14)</f>
@@ -20671,12 +20602,12 @@
         <v>충분</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B15" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A15)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A15)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A15)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A15)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A15)</f>
@@ -20694,12 +20625,12 @@
         <v>충분</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B16" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A16)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A16)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A16)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A16)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A16)</f>
@@ -20717,12 +20648,12 @@
         <v>충분</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B17" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A17)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A17)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A17)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A17)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A17)</f>
@@ -20740,35 +20671,35 @@
         <v>하한</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B18" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A18)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A18)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A18)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A18)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A18)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C18" s="4">
         <v>0</v>
       </c>
       <c r="D18" s="35">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E18" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>보완 필요</v>
+        <v>하한</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>73</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B19" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A19)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A19)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A19)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A19)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A19)</f>
@@ -20786,12 +20717,12 @@
         <v>충분</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B20" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A20)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A20)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A20)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A20)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A20)</f>
@@ -20809,12 +20740,12 @@
         <v>충분</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B21" s="7">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A21)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A21)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A21)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A21)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A21)</f>
@@ -20832,12 +20763,12 @@
         <v>충분</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B22" s="26">
         <f>SUMIFS(월_가슴!$E:$E,월_가슴!$C:$C,$A22)+SUMIFS(화_어깨!$E:$E,화_어깨!$C:$C,$A22)+SUMIFS(수_등!$E:$E,수_등!$C:$C,$A22)+SUMIFS(금_하체!$E:$E,금_하체!$C:$C,$A22)+SUMIFS(토_둔근팔복부!$E:$E,토_둔근팔복부!$C:$C,$A22)</f>
@@ -20855,16 +20786,16 @@
         <v>충분</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="24" customHeight="1">
       <c r="A23" s="36" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B23" s="15">
         <f>SUM(B5:B22)</f>
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -20873,22 +20804,22 @@
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="36" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16.5" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="36" customHeight="1">
@@ -20896,22 +20827,22 @@
     </row>
     <row r="29" spans="1:6" ht="48" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="48" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16.5" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="48" customHeight="1">
@@ -20919,17 +20850,17 @@
     </row>
     <row r="34" spans="1:1" ht="48" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1">
       <c r="A35" s="11" t="s">
-        <v>375</v>
+        <v>573</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="48" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -20937,32 +20868,32 @@
     </row>
     <row r="38" spans="1:1" ht="48">
       <c r="A38" s="11" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="45">
       <c r="A40" s="13" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="48">
       <c r="A41" s="11" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="48">
       <c r="A42" s="11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="60">
       <c r="A43" s="11" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="48">
       <c r="A44" s="11" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -20992,61 +20923,61 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="38" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="38" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="84" customHeight="1">
       <c r="A8" s="38" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
@@ -21054,39 +20985,39 @@
         <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>399</v>
-      </c>
       <c r="J9" s="5" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="16">
@@ -21410,17 +21341,17 @@
     </row>
     <row r="23" spans="1:11" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="120" customHeight="1">
@@ -21428,27 +21359,27 @@
     </row>
     <row r="27" spans="1:11" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
